--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/38.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/38.xlsx
@@ -426,13 +426,13 @@
         <v>-14.43380598970761</v>
       </c>
       <c r="E2">
-        <v>-5.122478005723273</v>
+        <v>-7.546371045908383</v>
       </c>
       <c r="F2">
-        <v>3.305960313444137</v>
+        <v>3.769837775337832</v>
       </c>
       <c r="G2">
-        <v>-16.36394813634007</v>
+        <v>-19.20087001630142</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-13.80073861475221</v>
       </c>
       <c r="E3">
-        <v>-6.068886883157253</v>
+        <v>-7.511708344191363</v>
       </c>
       <c r="F3">
-        <v>3.576947455391551</v>
+        <v>3.669693126543789</v>
       </c>
       <c r="G3">
-        <v>-16.26350495968617</v>
+        <v>-19.00752022994201</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-12.93011212557403</v>
       </c>
       <c r="E4">
-        <v>-6.756546541843089</v>
+        <v>-8.898374234902468</v>
       </c>
       <c r="F4">
-        <v>3.631314864772088</v>
+        <v>3.656647996684502</v>
       </c>
       <c r="G4">
-        <v>-15.53444408963942</v>
+        <v>-18.09755956180473</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-11.9111366621523</v>
       </c>
       <c r="E5">
-        <v>-7.676349947530216</v>
+        <v>-9.19199381593387</v>
       </c>
       <c r="F5">
-        <v>3.687070617919717</v>
+        <v>3.969873592500663</v>
       </c>
       <c r="G5">
-        <v>-14.63899916142872</v>
+        <v>-17.53350558215011</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-10.77758600852013</v>
       </c>
       <c r="E6">
-        <v>-11.16496854937102</v>
+        <v>-10.31913799059041</v>
       </c>
       <c r="F6">
-        <v>3.966874902502528</v>
+        <v>4.183946923671333</v>
       </c>
       <c r="G6">
-        <v>-13.98655972901426</v>
+        <v>-16.79708502310101</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-9.587916717420622</v>
       </c>
       <c r="E7">
-        <v>-10.83173148551208</v>
+        <v>-10.30949008068284</v>
       </c>
       <c r="F7">
-        <v>3.731593709085385</v>
+        <v>4.053126173216818</v>
       </c>
       <c r="G7">
-        <v>-12.96716317447899</v>
+        <v>-16.30912641604358</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-8.391880395622049</v>
       </c>
       <c r="E8">
-        <v>-11.36594244537947</v>
+        <v>-11.57495695851279</v>
       </c>
       <c r="F8">
-        <v>3.588377268815378</v>
+        <v>4.525910241425414</v>
       </c>
       <c r="G8">
-        <v>-12.31083503799606</v>
+        <v>-15.5773399286437</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-7.228702543294637</v>
       </c>
       <c r="E9">
-        <v>-10.55023097512652</v>
+        <v>-11.33338957501547</v>
       </c>
       <c r="F9">
-        <v>3.95773801004965</v>
+        <v>4.62649061147333</v>
       </c>
       <c r="G9">
-        <v>-12.30937171565274</v>
+        <v>-14.3565662008175</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-6.136057333237432</v>
       </c>
       <c r="E10">
-        <v>-11.75005634796756</v>
+        <v>-12.86497762169514</v>
       </c>
       <c r="F10">
-        <v>4.569195751691299</v>
+        <v>4.555444852804827</v>
       </c>
       <c r="G10">
-        <v>-11.20164192324944</v>
+        <v>-13.95588739618557</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-5.12388963536826</v>
       </c>
       <c r="E11">
-        <v>-11.61505206064269</v>
+        <v>-13.11470191223443</v>
       </c>
       <c r="F11">
-        <v>4.752680788146195</v>
+        <v>4.728220755476332</v>
       </c>
       <c r="G11">
-        <v>-10.95074675729887</v>
+        <v>-13.29106389680316</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-4.210116190981972</v>
       </c>
       <c r="E12">
-        <v>-12.99367733422893</v>
+        <v>-13.8354211330659</v>
       </c>
       <c r="F12">
-        <v>4.918099131546034</v>
+        <v>5.158002615070799</v>
       </c>
       <c r="G12">
-        <v>-10.23689086375076</v>
+        <v>-12.27323639976714</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-3.381064510488717</v>
       </c>
       <c r="E13">
-        <v>-13.63437663246492</v>
+        <v>-14.58992257481353</v>
       </c>
       <c r="F13">
-        <v>5.091479742421582</v>
+        <v>5.237146493469069</v>
       </c>
       <c r="G13">
-        <v>-10.28370412501401</v>
+        <v>-11.51019668886705</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-2.63879657813842</v>
       </c>
       <c r="E14">
-        <v>-15.1125211558167</v>
+        <v>-15.71481986214334</v>
       </c>
       <c r="F14">
-        <v>5.224323366073733</v>
+        <v>5.459483617850068</v>
       </c>
       <c r="G14">
-        <v>-7.915312343549182</v>
+        <v>-10.97428000904316</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-1.960543930552137</v>
       </c>
       <c r="E15">
-        <v>-14.76123008232873</v>
+        <v>-16.0547851283485</v>
       </c>
       <c r="F15">
-        <v>5.21066690107118</v>
+        <v>5.483870754188485</v>
       </c>
       <c r="G15">
-        <v>-8.791881588366127</v>
+        <v>-10.80928486700169</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-1.334516717779278</v>
       </c>
       <c r="E16">
-        <v>-16.83237011863952</v>
+        <v>-17.66706591785827</v>
       </c>
       <c r="F16">
-        <v>5.105273716413</v>
+        <v>6.002521525490089</v>
       </c>
       <c r="G16">
-        <v>-8.08427190125226</v>
+        <v>-9.564570611274972</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-0.7398768224604476</v>
       </c>
       <c r="E17">
-        <v>-17.03498037990996</v>
+        <v>-18.3796489977044</v>
       </c>
       <c r="F17">
-        <v>6.135524195683578</v>
+        <v>6.222244322347852</v>
       </c>
       <c r="G17">
-        <v>-7.732378775422169</v>
+        <v>-8.868787597158846</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-0.1649782765806775</v>
       </c>
       <c r="E18">
-        <v>-18.42758536281557</v>
+        <v>-18.9887838898717</v>
       </c>
       <c r="F18">
-        <v>5.750149455818386</v>
+        <v>6.320387635496733</v>
       </c>
       <c r="G18">
-        <v>-6.313741936524668</v>
+        <v>-8.789995325399047</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>0.3944436763171071</v>
       </c>
       <c r="E19">
-        <v>-20.17822208118935</v>
+        <v>-19.77261115678394</v>
       </c>
       <c r="F19">
-        <v>6.522003977664104</v>
+        <v>6.528650797704167</v>
       </c>
       <c r="G19">
-        <v>-6.287548336042028</v>
+        <v>-8.123064955131612</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>0.9363705362493111</v>
       </c>
       <c r="E20">
-        <v>-18.20969543708109</v>
+        <v>-21.09596549405936</v>
       </c>
       <c r="F20">
-        <v>6.295495195042608</v>
+        <v>6.828592693849035</v>
       </c>
       <c r="G20">
-        <v>-6.820195058265552</v>
+        <v>-8.049466759735834</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>1.445901396289927</v>
       </c>
       <c r="E21">
-        <v>-20.96621917227172</v>
+        <v>-21.15859176762645</v>
       </c>
       <c r="F21">
-        <v>6.4684748760952</v>
+        <v>6.605988835164335</v>
       </c>
       <c r="G21">
-        <v>-6.253480729872591</v>
+        <v>-7.20330877328847</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>1.910746817434813</v>
       </c>
       <c r="E22">
-        <v>-19.72595813397214</v>
+        <v>-21.6933966367133</v>
       </c>
       <c r="F22">
-        <v>6.771432029586258</v>
+        <v>6.66668497150226</v>
       </c>
       <c r="G22">
-        <v>-6.388842615432632</v>
+        <v>-7.353781648541876</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>2.310037793677069</v>
       </c>
       <c r="E23">
-        <v>-21.76408014025055</v>
+        <v>-21.89640975948224</v>
       </c>
       <c r="F23">
-        <v>6.816448827723994</v>
+        <v>6.584524179022994</v>
       </c>
       <c r="G23">
-        <v>-5.82318041710989</v>
+        <v>-6.848101307199961</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>2.634184300240141</v>
       </c>
       <c r="E24">
-        <v>-21.56336374334424</v>
+        <v>-22.19041558916685</v>
       </c>
       <c r="F24">
-        <v>7.358491037745851</v>
+        <v>6.55610786363736</v>
       </c>
       <c r="G24">
-        <v>-5.542454883461252</v>
+        <v>-6.645980071700563</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>2.871670801910323</v>
       </c>
       <c r="E25">
-        <v>-21.36100267475329</v>
+        <v>-22.51426639543168</v>
       </c>
       <c r="F25">
-        <v>6.466349285339617</v>
+        <v>6.527134885357044</v>
       </c>
       <c r="G25">
-        <v>-5.122226823331066</v>
+        <v>-6.661521834251459</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>3.025681819877484</v>
       </c>
       <c r="E26">
-        <v>-20.45128741937418</v>
+        <v>-22.98526132572387</v>
       </c>
       <c r="F26">
-        <v>7.038320409624619</v>
+        <v>6.329794575722924</v>
       </c>
       <c r="G26">
-        <v>-5.303642243478346</v>
+        <v>-6.366241399507365</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>3.101586964624446</v>
       </c>
       <c r="E27">
-        <v>-21.70125035932855</v>
+        <v>-23.19773546389077</v>
       </c>
       <c r="F27">
-        <v>6.666834077634764</v>
+        <v>6.284761210237131</v>
       </c>
       <c r="G27">
-        <v>-5.636219775451085</v>
+        <v>-6.156833575854168</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>3.115076351310462</v>
       </c>
       <c r="E28">
-        <v>-21.04375547449494</v>
+        <v>-23.43638729303807</v>
       </c>
       <c r="F28">
-        <v>6.790915230900102</v>
+        <v>6.289698279957816</v>
       </c>
       <c r="G28">
-        <v>-5.524412027592068</v>
+        <v>-6.133493519209615</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>3.082361438301981</v>
       </c>
       <c r="E29">
-        <v>-23.01191663600661</v>
+        <v>-22.68799107193794</v>
       </c>
       <c r="F29">
-        <v>6.8482597927263</v>
+        <v>6.117439278545659</v>
       </c>
       <c r="G29">
-        <v>-5.19849711581585</v>
+        <v>-6.397922785120524</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>3.022940911244412</v>
       </c>
       <c r="E30">
-        <v>-22.54243347463667</v>
+        <v>-23.30374618295702</v>
       </c>
       <c r="F30">
-        <v>7.292601037792372</v>
+        <v>6.126041045656329</v>
       </c>
       <c r="G30">
-        <v>-5.699859285604063</v>
+        <v>-5.997977599718698</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>2.955216399175982</v>
       </c>
       <c r="E31">
-        <v>-21.51362903772942</v>
+        <v>-23.1544673083087</v>
       </c>
       <c r="F31">
-        <v>6.706776297062951</v>
+        <v>6.222055454580015</v>
       </c>
       <c r="G31">
-        <v>-5.658847098822265</v>
+        <v>-6.483315019206658</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>2.894160130831441</v>
       </c>
       <c r="E32">
-        <v>-21.43049835985165</v>
+        <v>-22.09672744810137</v>
       </c>
       <c r="F32">
-        <v>6.3354688924321</v>
+        <v>6.130452930443639</v>
       </c>
       <c r="G32">
-        <v>-5.23590125357273</v>
+        <v>-6.379266404272429</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>2.850517314128991</v>
       </c>
       <c r="E33">
-        <v>-21.45911398587972</v>
+        <v>-22.65597396583483</v>
       </c>
       <c r="F33">
-        <v>6.452482415016753</v>
+        <v>6.268475507098093</v>
       </c>
       <c r="G33">
-        <v>-6.161867091425835</v>
+        <v>-6.891601533577091</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>2.82761867357106</v>
       </c>
       <c r="E34">
-        <v>-20.28472703240325</v>
+        <v>-22.51454881380177</v>
       </c>
       <c r="F34">
-        <v>6.448509564952927</v>
+        <v>6.207057034384927</v>
       </c>
       <c r="G34">
-        <v>-5.873943734939497</v>
+        <v>-6.842691844407175</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>2.824377218285413</v>
       </c>
       <c r="E35">
-        <v>-20.52486986441616</v>
+        <v>-21.69473812397122</v>
       </c>
       <c r="F35">
-        <v>6.563250047384297</v>
+        <v>6.532529213884075</v>
       </c>
       <c r="G35">
-        <v>-6.095635111893881</v>
+        <v>-7.247882015692548</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>2.833632503431646</v>
       </c>
       <c r="E36">
-        <v>-19.27557143827376</v>
+        <v>-21.40627683140525</v>
       </c>
       <c r="F36">
-        <v>6.407715783834662</v>
+        <v>6.472300276761328</v>
       </c>
       <c r="G36">
-        <v>-6.533569241840998</v>
+        <v>-7.163233843814882</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>2.845943542169989</v>
       </c>
       <c r="E37">
-        <v>-19.86063016439103</v>
+        <v>-21.79755087031735</v>
       </c>
       <c r="F37">
-        <v>6.534775746280467</v>
+        <v>6.379438634172698</v>
       </c>
       <c r="G37">
-        <v>-6.456575773104476</v>
+        <v>-7.561126983968093</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>2.850523970239876</v>
       </c>
       <c r="E38">
-        <v>-18.76765445930386</v>
+        <v>-20.59876795351884</v>
       </c>
       <c r="F38">
-        <v>6.266214064088451</v>
+        <v>6.545450088632942</v>
       </c>
       <c r="G38">
-        <v>-6.259297468821591</v>
+        <v>-7.730780999732408</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>2.835525492594155</v>
       </c>
       <c r="E39">
-        <v>-19.3914501874478</v>
+        <v>-20.05135393484981</v>
       </c>
       <c r="F39">
-        <v>7.164129537292197</v>
+        <v>6.689102250156821</v>
       </c>
       <c r="G39">
-        <v>-5.910350568262571</v>
+        <v>-8.012152692667346</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>2.793013179399299</v>
       </c>
       <c r="E40">
-        <v>-18.45442341439661</v>
+        <v>-19.9448988221718</v>
       </c>
       <c r="F40">
-        <v>6.571157642611421</v>
+        <v>6.749044572158199</v>
       </c>
       <c r="G40">
-        <v>-7.104492090514833</v>
+        <v>-8.679538637865932</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>2.715171345944099</v>
       </c>
       <c r="E41">
-        <v>-17.80118141795963</v>
+        <v>-18.97728364771325</v>
       </c>
       <c r="F41">
-        <v>6.763060548613566</v>
+        <v>6.946813976106969</v>
       </c>
       <c r="G41">
-        <v>-7.101638546676746</v>
+        <v>-8.42788374523934</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>2.601355324469677</v>
       </c>
       <c r="E42">
-        <v>-16.49555298661858</v>
+        <v>-19.23876567951313</v>
       </c>
       <c r="F42">
-        <v>6.788025885399137</v>
+        <v>6.962001264069896</v>
       </c>
       <c r="G42">
-        <v>-6.991472957165539</v>
+        <v>-8.781030028473165</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>2.45063650236255</v>
       </c>
       <c r="E43">
-        <v>-16.19905523013907</v>
+        <v>-18.35302691311225</v>
       </c>
       <c r="F43">
-        <v>7.057280082739894</v>
+        <v>7.025679523057899</v>
       </c>
       <c r="G43">
-        <v>-7.341827049059169</v>
+        <v>-9.229880986928022</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>2.268143729460374</v>
       </c>
       <c r="E44">
-        <v>-15.63546030014851</v>
+        <v>-17.81792301281001</v>
       </c>
       <c r="F44">
-        <v>6.820078733683062</v>
+        <v>6.946701318140188</v>
       </c>
       <c r="G44">
-        <v>-7.379077152885173</v>
+        <v>-9.306407132382734</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>2.058325543694735</v>
       </c>
       <c r="E45">
-        <v>-13.54097090976953</v>
+        <v>-17.1249472436284</v>
       </c>
       <c r="F45">
-        <v>6.920589520869142</v>
+        <v>6.910551364682018</v>
       </c>
       <c r="G45">
-        <v>-7.124409461000436</v>
+        <v>-9.308755497142441</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>1.828531345738659</v>
       </c>
       <c r="E46">
-        <v>-15.02114220024782</v>
+        <v>-16.21632012961638</v>
       </c>
       <c r="F46">
-        <v>6.652526515853611</v>
+        <v>7.038081839812613</v>
       </c>
       <c r="G46">
-        <v>-7.247187557631312</v>
+        <v>-9.42740470120247</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>1.585331488090492</v>
       </c>
       <c r="E47">
-        <v>-14.11559676903883</v>
+        <v>-15.39855697296897</v>
       </c>
       <c r="F47">
-        <v>6.569479370253349</v>
+        <v>7.110471210408456</v>
       </c>
       <c r="G47">
-        <v>-7.832778874790318</v>
+        <v>-9.46606330173538</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>1.334442605289059</v>
       </c>
       <c r="E48">
-        <v>-12.68746936967197</v>
+        <v>-15.58231580803601</v>
       </c>
       <c r="F48">
-        <v>6.717480460641926</v>
+        <v>7.114440747002671</v>
       </c>
       <c r="G48">
-        <v>-8.003535930144377</v>
+        <v>-9.735298948438528</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>1.081321981470285</v>
       </c>
       <c r="E49">
-        <v>-12.98852735218614</v>
+        <v>-14.31742207336888</v>
       </c>
       <c r="F49">
-        <v>6.709884331558254</v>
+        <v>7.121501750744135</v>
       </c>
       <c r="G49">
-        <v>-8.113568371681438</v>
+        <v>-9.833365042142221</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>0.8272724222955036</v>
       </c>
       <c r="E50">
-        <v>-12.36125953937463</v>
+        <v>-14.28494811402004</v>
       </c>
       <c r="F50">
-        <v>6.464455637456817</v>
+        <v>7.046340662818524</v>
       </c>
       <c r="G50">
-        <v>-8.3309481039436</v>
+        <v>-9.975072342430964</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>0.5759640695843198</v>
       </c>
       <c r="E51">
-        <v>-12.21107111144618</v>
+        <v>-13.96669168340975</v>
       </c>
       <c r="F51">
-        <v>6.14036848825515</v>
+        <v>6.901071528124381</v>
       </c>
       <c r="G51">
-        <v>-7.718885142003001</v>
+        <v>-9.820205584030715</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>0.3254018566605888</v>
       </c>
       <c r="E52">
-        <v>-12.59419654973897</v>
+        <v>-13.74120138095084</v>
       </c>
       <c r="F52">
-        <v>5.783519408272761</v>
+        <v>7.083603942066057</v>
       </c>
       <c r="G52">
-        <v>-7.754314251476703</v>
+        <v>-10.23069034534686</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>0.07850320161798113</v>
       </c>
       <c r="E53">
-        <v>-11.15551168718438</v>
+        <v>-12.85989409103355</v>
       </c>
       <c r="F53">
-        <v>6.513024475017757</v>
+        <v>6.538828119614962</v>
       </c>
       <c r="G53">
-        <v>-8.082517480887033</v>
+        <v>-10.8752923224988</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-0.1671538743187671</v>
       </c>
       <c r="E54">
-        <v>-10.78357500020069</v>
+        <v>-12.62262528125742</v>
       </c>
       <c r="F54">
-        <v>6.578654367606757</v>
+        <v>7.211472391096994</v>
       </c>
       <c r="G54">
-        <v>-8.266247326114334</v>
+        <v>-10.17203083050144</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-0.4076047912737734</v>
       </c>
       <c r="E55">
-        <v>-10.70626712460033</v>
+        <v>-12.02805985441761</v>
       </c>
       <c r="F55">
-        <v>6.363489248199197</v>
+        <v>6.924307233772907</v>
       </c>
       <c r="G55">
-        <v>-8.699346357078708</v>
+        <v>-10.85902477295158</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-0.6435301890306205</v>
       </c>
       <c r="E56">
-        <v>-9.985489758810312</v>
+        <v>-11.69623072919779</v>
       </c>
       <c r="F56">
-        <v>5.818199837958366</v>
+        <v>6.477976250205311</v>
       </c>
       <c r="G56">
-        <v>-8.54879515948757</v>
+        <v>-10.92150902862299</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-0.870072551044709</v>
       </c>
       <c r="E57">
-        <v>-10.19058779366432</v>
+        <v>-11.68858051393745</v>
       </c>
       <c r="F57">
-        <v>6.002871096534071</v>
+        <v>6.683946491441796</v>
       </c>
       <c r="G57">
-        <v>-8.092238588372043</v>
+        <v>-10.85137137518273</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-1.086806671494468</v>
       </c>
       <c r="E58">
-        <v>-10.72013885042526</v>
+        <v>-11.01714745189772</v>
       </c>
       <c r="F58">
-        <v>6.173484960284268</v>
+        <v>6.600311204985547</v>
       </c>
       <c r="G58">
-        <v>-9.789927473635279</v>
+        <v>-11.26353092915408</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-1.291320815291031</v>
       </c>
       <c r="E59">
-        <v>-8.746453917851564</v>
+        <v>-10.52671133939402</v>
       </c>
       <c r="F59">
-        <v>5.915905773118568</v>
+        <v>6.892782883891969</v>
       </c>
       <c r="G59">
-        <v>-8.671229943204713</v>
+        <v>-11.34488434135776</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-1.48303300133415</v>
       </c>
       <c r="E60">
-        <v>-8.520461076822343</v>
+        <v>-10.22138385563792</v>
       </c>
       <c r="F60">
-        <v>6.106665532104849</v>
+        <v>6.559043597712881</v>
       </c>
       <c r="G60">
-        <v>-9.402153579517222</v>
+        <v>-10.97351114476108</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-1.661140413377008</v>
       </c>
       <c r="E61">
-        <v>-8.010131082072713</v>
+        <v>-9.923756425678061</v>
       </c>
       <c r="F61">
-        <v>5.85884285620932</v>
+        <v>6.872666809882385</v>
       </c>
       <c r="G61">
-        <v>-9.56758210516082</v>
+        <v>-11.6228764254195</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-1.824503549397255</v>
       </c>
       <c r="E62">
-        <v>-9.721137857984976</v>
+        <v>-9.627574313259238</v>
       </c>
       <c r="F62">
-        <v>5.515612136328957</v>
+        <v>6.501851455488798</v>
       </c>
       <c r="G62">
-        <v>-9.440565464686273</v>
+        <v>-11.61563813604064</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-1.973924747085911</v>
       </c>
       <c r="E63">
-        <v>-8.244459418230862</v>
+        <v>-9.37512551609086</v>
       </c>
       <c r="F63">
-        <v>6.012278036760262</v>
+        <v>6.897584101358595</v>
       </c>
       <c r="G63">
-        <v>-9.953665542156131</v>
+        <v>-11.71461276886204</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-2.107602568620448</v>
       </c>
       <c r="E64">
-        <v>-6.924959261064886</v>
+        <v>-9.600781947002769</v>
       </c>
       <c r="F64">
-        <v>6.050427669128791</v>
+        <v>6.607420254036373</v>
       </c>
       <c r="G64">
-        <v>-9.506665601616374</v>
+        <v>-12.10787444811062</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-2.226648449504734</v>
       </c>
       <c r="E65">
-        <v>-7.638829836421715</v>
+        <v>-8.764100912770761</v>
       </c>
       <c r="F65">
-        <v>6.133564278408555</v>
+        <v>6.536861575400716</v>
       </c>
       <c r="G65">
-        <v>-9.804430159838914</v>
+        <v>-11.98740686044288</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-2.328694162626823</v>
       </c>
       <c r="E66">
-        <v>-9.261709621232443</v>
+        <v>-9.041165793461397</v>
       </c>
       <c r="F66">
-        <v>5.431266110641106</v>
+        <v>6.290399078780585</v>
       </c>
       <c r="G66">
-        <v>-9.7982348629242</v>
+        <v>-11.89140194959387</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-2.415248584011571</v>
       </c>
       <c r="E67">
-        <v>-6.971695348103182</v>
+        <v>-8.634358744194442</v>
       </c>
       <c r="F67">
-        <v>6.142851933728743</v>
+        <v>6.433535995779923</v>
       </c>
       <c r="G67">
-        <v>-10.35327655225029</v>
+        <v>-11.76083861259229</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-2.485252947855487</v>
       </c>
       <c r="E68">
-        <v>-8.215046375628427</v>
+        <v>-9.204872924252165</v>
       </c>
       <c r="F68">
-        <v>5.768714826049929</v>
+        <v>6.532469571431073</v>
       </c>
       <c r="G68">
-        <v>-10.13077062298348</v>
+        <v>-12.11510882137259</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-2.540419473307343</v>
       </c>
       <c r="E69">
-        <v>-7.60915929471714</v>
+        <v>-9.129326010253532</v>
       </c>
       <c r="F69">
-        <v>5.809366127974912</v>
+        <v>6.680068075261889</v>
       </c>
       <c r="G69">
-        <v>-10.68101245837881</v>
+        <v>-12.07608863271381</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-2.581784005770682</v>
       </c>
       <c r="E70">
-        <v>-6.573917380256404</v>
+        <v>-8.276156727061954</v>
       </c>
       <c r="F70">
-        <v>6.062366100137937</v>
+        <v>6.757536994771699</v>
       </c>
       <c r="G70">
-        <v>-9.618951115735566</v>
+        <v>-11.35910898326244</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-2.611595269046249</v>
       </c>
       <c r="E71">
-        <v>-7.672180123360088</v>
+        <v>-9.083723749906916</v>
       </c>
       <c r="F71">
-        <v>5.47406619760895</v>
+        <v>6.170883886639478</v>
       </c>
       <c r="G71">
-        <v>-9.766556088055632</v>
+        <v>-11.70844357939324</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-2.632273982170324</v>
       </c>
       <c r="E72">
-        <v>-7.368696665432218</v>
+        <v>-8.247387432214866</v>
       </c>
       <c r="F72">
-        <v>5.968921286897736</v>
+        <v>6.657259807193207</v>
       </c>
       <c r="G72">
-        <v>-9.843472539826717</v>
+        <v>-11.49176483205379</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-2.645240896131635</v>
       </c>
       <c r="E73">
-        <v>-8.060742115277073</v>
+        <v>-8.410729080409048</v>
       </c>
       <c r="F73">
-        <v>5.844190693588603</v>
+        <v>6.614477944308224</v>
       </c>
       <c r="G73">
-        <v>-9.167809228902007</v>
+        <v>-11.2467490629224</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-2.652526325250226</v>
       </c>
       <c r="E74">
-        <v>-7.923391263553667</v>
+        <v>-8.366136050414365</v>
       </c>
       <c r="F74">
-        <v>5.813080527409065</v>
+        <v>6.659405278766458</v>
       </c>
       <c r="G74">
-        <v>-9.233643069883815</v>
+        <v>-11.38800600976918</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-2.654853392194314</v>
       </c>
       <c r="E75">
-        <v>-7.99698616822963</v>
+        <v>-8.85603224544584</v>
       </c>
       <c r="F75">
-        <v>5.715122768558413</v>
+        <v>6.137618308477855</v>
       </c>
       <c r="G75">
-        <v>-9.413288405198321</v>
+        <v>-11.30086718755159</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-2.653649430029664</v>
       </c>
       <c r="E76">
-        <v>-8.455575456294547</v>
+        <v>-9.206604813374618</v>
       </c>
       <c r="F76">
-        <v>5.624650137559455</v>
+        <v>6.541371207541556</v>
       </c>
       <c r="G76">
-        <v>-9.977292780705707</v>
+        <v>-10.90141543287749</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-2.647815191889391</v>
       </c>
       <c r="E77">
-        <v>-8.546410341179872</v>
+        <v>-9.465636450492848</v>
       </c>
       <c r="F77">
-        <v>5.536934313277016</v>
+        <v>6.569446235557238</v>
       </c>
       <c r="G77">
-        <v>-9.084645265324388</v>
+        <v>-10.80876141271117</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-2.634358853878394</v>
       </c>
       <c r="E78">
-        <v>-8.490491503902382</v>
+        <v>-10.24287257103259</v>
       </c>
       <c r="F78">
-        <v>5.64937359106341</v>
+        <v>6.725658103642362</v>
       </c>
       <c r="G78">
-        <v>-8.956408101753496</v>
+        <v>-10.60987097364327</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-2.60820574565128</v>
       </c>
       <c r="E79">
-        <v>-8.901821400302074</v>
+        <v>-10.14708290503674</v>
       </c>
       <c r="F79">
-        <v>5.28690486662043</v>
+        <v>6.454059626551683</v>
       </c>
       <c r="G79">
-        <v>-9.097995307791047</v>
+        <v>-10.50136712306431</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-2.561952827211484</v>
       </c>
       <c r="E80">
-        <v>-11.11413324275512</v>
+        <v>-11.1908264430794</v>
       </c>
       <c r="F80">
-        <v>5.510191300045037</v>
+        <v>6.358287100909616</v>
       </c>
       <c r="G80">
-        <v>-7.532414014955029</v>
+        <v>-10.38236285773989</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-2.488811850073256</v>
       </c>
       <c r="E81">
-        <v>-9.550166760587084</v>
+        <v>-11.62587532935519</v>
       </c>
       <c r="F81">
-        <v>5.228826371275352</v>
+        <v>6.752556849946068</v>
       </c>
       <c r="G81">
-        <v>-8.818445914580705</v>
+        <v>-10.19208395970578</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-2.379596848376083</v>
       </c>
       <c r="E82">
-        <v>-11.01569382793403</v>
+        <v>-12.12336774789978</v>
       </c>
       <c r="F82">
-        <v>5.768736363602402</v>
+        <v>6.649458242993641</v>
       </c>
       <c r="G82">
-        <v>-8.191754950696099</v>
+        <v>-9.655073377898209</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-2.230041549521235</v>
       </c>
       <c r="E83">
-        <v>-12.84040307028613</v>
+        <v>-13.21150080858221</v>
       </c>
       <c r="F83">
-        <v>5.85943762400453</v>
+        <v>6.528801560571477</v>
       </c>
       <c r="G83">
-        <v>-7.951989388937437</v>
+        <v>-9.539745040958074</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-2.03405119436151</v>
       </c>
       <c r="E84">
-        <v>-14.43541065389593</v>
+        <v>-13.81288580841738</v>
       </c>
       <c r="F84">
-        <v>6.039726819019426</v>
+        <v>6.944136692661121</v>
       </c>
       <c r="G84">
-        <v>-8.496110333638903</v>
+        <v>-9.671611139510615</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-1.793009394362942</v>
       </c>
       <c r="E85">
-        <v>-14.66533658604976</v>
+        <v>-15.4504513484727</v>
       </c>
       <c r="F85">
-        <v>5.624461269791618</v>
+        <v>6.613538575673449</v>
       </c>
       <c r="G85">
-        <v>-7.759165014926992</v>
+        <v>-9.427558735133346</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-1.507004504279477</v>
       </c>
       <c r="E86">
-        <v>-16.93382476488244</v>
+        <v>-15.74916276658834</v>
       </c>
       <c r="F86">
-        <v>5.387389146049621</v>
+        <v>6.624174813125395</v>
       </c>
       <c r="G86">
-        <v>-8.656934811196074</v>
+        <v>-9.759671554568866</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-1.183822936005463</v>
       </c>
       <c r="E87">
-        <v>-16.46535083386443</v>
+        <v>-17.06348802244359</v>
       </c>
       <c r="F87">
-        <v>5.307887412933342</v>
+        <v>6.543597859120282</v>
       </c>
       <c r="G87">
-        <v>-7.867256367860559</v>
+        <v>-9.085227461368207</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-0.831791079747886</v>
       </c>
       <c r="E88">
-        <v>-18.99968191638805</v>
+        <v>-19.83919959395492</v>
       </c>
       <c r="F88">
-        <v>5.537002239404045</v>
+        <v>6.910428766306404</v>
       </c>
       <c r="G88">
-        <v>-6.985110572596996</v>
+        <v>-9.062641909910486</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-0.4646674773020827</v>
       </c>
       <c r="E89">
-        <v>-20.0854767190946</v>
+        <v>-20.06519243498414</v>
       </c>
       <c r="F89">
-        <v>5.541916114837452</v>
+        <v>6.811082663688659</v>
       </c>
       <c r="G89">
-        <v>-7.279299716102005</v>
+        <v>-8.257248089508767</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-0.09753206810605074</v>
       </c>
       <c r="E90">
-        <v>-22.16569567536147</v>
+        <v>-21.69171043291542</v>
       </c>
       <c r="F90">
-        <v>5.802518843023371</v>
+        <v>6.916613357335705</v>
       </c>
       <c r="G90">
-        <v>-6.337006281576078</v>
+        <v>-8.395152840300552</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>0.2541925207457655</v>
       </c>
       <c r="E91">
-        <v>-24.39160513169201</v>
+        <v>-23.38503698821788</v>
       </c>
       <c r="F91">
-        <v>5.627703499806175</v>
+        <v>7.055936470812553</v>
       </c>
       <c r="G91">
-        <v>-6.941646896644142</v>
+        <v>-8.008745670975944</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>0.5752087712111106</v>
       </c>
       <c r="E92">
-        <v>-25.19310015958007</v>
+        <v>-25.33983311568626</v>
       </c>
       <c r="F92">
-        <v>5.220991672379673</v>
+        <v>6.776206739295994</v>
       </c>
       <c r="G92">
-        <v>-7.060639413617903</v>
+        <v>-8.080827023764286</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>0.8565711117658006</v>
       </c>
       <c r="E93">
-        <v>-27.43271936649386</v>
+        <v>-27.99707018094553</v>
       </c>
       <c r="F93">
-        <v>5.525050554516454</v>
+        <v>6.590531499428096</v>
       </c>
       <c r="G93">
-        <v>-7.114715766333632</v>
+        <v>-8.208677797135694</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>1.090452462635455</v>
       </c>
       <c r="E94">
-        <v>-30.17195120633356</v>
+        <v>-30.08834083254778</v>
       </c>
       <c r="F94">
-        <v>5.618394306933514</v>
+        <v>6.829595018406422</v>
       </c>
       <c r="G94">
-        <v>-7.423373656362592</v>
+        <v>-8.014498446682461</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>1.27981426078044</v>
       </c>
       <c r="E95">
-        <v>-33.07000184723471</v>
+        <v>-32.19359534668072</v>
       </c>
       <c r="F95">
-        <v>5.108966578294679</v>
+        <v>6.359912357753908</v>
       </c>
       <c r="G95">
-        <v>-6.078354593445303</v>
+        <v>-7.808025099949677</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>1.426167422076722</v>
       </c>
       <c r="E96">
-        <v>-34.39044478337142</v>
+        <v>-34.26759486898865</v>
       </c>
       <c r="F96">
-        <v>4.52085223006392</v>
+        <v>6.012181946141538</v>
       </c>
       <c r="G96">
-        <v>-6.092893830073213</v>
+        <v>-7.608261366816053</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>1.540503092024986</v>
       </c>
       <c r="E97">
-        <v>-36.86757160971252</v>
+        <v>-36.57680320825561</v>
       </c>
       <c r="F97">
-        <v>5.684287620356604</v>
+        <v>5.705917949978504</v>
       </c>
       <c r="G97">
-        <v>-6.326558081722442</v>
+        <v>-7.567102978337152</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>1.629658731850546</v>
       </c>
       <c r="E98">
-        <v>-39.7176360469666</v>
+        <v>-39.36222291123873</v>
       </c>
       <c r="F98">
-        <v>5.042838008529195</v>
+        <v>5.976267249025762</v>
       </c>
       <c r="G98">
-        <v>-6.37326430245746</v>
+        <v>-7.826255929429421</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>1.709217786192721</v>
       </c>
       <c r="E99">
-        <v>-42.45658339183055</v>
+        <v>-42.06079481220836</v>
       </c>
       <c r="F99">
-        <v>4.396635224544523</v>
+        <v>5.50359086857953</v>
       </c>
       <c r="G99">
-        <v>-6.914938979477053</v>
+        <v>-7.490511564267661</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>1.786453795180222</v>
       </c>
       <c r="E100">
-        <v>-45.0243499021247</v>
+        <v>-44.15372259512921</v>
       </c>
       <c r="F100">
-        <v>4.58523957154872</v>
+        <v>5.596530377704024</v>
       </c>
       <c r="G100">
-        <v>-5.617182225892687</v>
+        <v>-7.245707265448151</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>1.875844460302804</v>
       </c>
       <c r="E101">
-        <v>-47.04900823559085</v>
+        <v>-46.72464866093873</v>
       </c>
       <c r="F101">
-        <v>3.898721802804602</v>
+        <v>5.296470853387959</v>
       </c>
       <c r="G101">
-        <v>-6.373214698310228</v>
+        <v>-7.448389811034639</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>1.976569420943465</v>
       </c>
       <c r="E102">
-        <v>-49.77370695070215</v>
+        <v>-49.39859824856912</v>
       </c>
       <c r="F102">
-        <v>4.14951831767618</v>
+        <v>4.657794615625123</v>
       </c>
       <c r="G102">
-        <v>-6.614309129065767</v>
+        <v>-7.442215400076656</v>
       </c>
     </row>
   </sheetData>
